--- a/tests/fixtures/control-sheet-cases.xlsx
+++ b/tests/fixtures/control-sheet-cases.xlsx
@@ -2,7 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Controle" sheetId="1" r:id="rId1"/>
+    <sheet name="Resumo" sheetId="1" r:id="rId1"/>
+    <sheet name="LV e Site" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -18,12 +19,15 @@
   <borders count="1">
     <border/>
   </borders>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+  </numFmts>
   <cellStyleXfs count="1">
     <xf/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0"/>
-    <xf numFmtId="14" applyNumberFormat="1"/>
+    <xf numFmtId="164" applyNumberFormat="1"/>
   </cellXfs>
 </styleSheet>
 </file>
@@ -34,6 +38,20 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Resumo</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
           <t> Titulo </t>
         </is>
       </c>
@@ -391,46 +409,138 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>011547/2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>72-2026</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Implantacao de Loja Virtual</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>18573230000105</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>CASA NOSSA</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Christian Albuquerque Alonso</t>
         </is>
       </c>
-      <c r="G9" s="1">
+      <c r="G10" s="1">
         <v>46133</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>https://out-of-scope.example/</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>012000/2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>80-2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Insercao digital - Desenvolvimento de WebSite</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>CNPJ INVALIDO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bruno Henrique Santana Leal</t>
+        </is>
+      </c>
+      <c r="G11" s="1">
+        <v>46150</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://invalid-cnpj.example/</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>012001/2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>81-2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Insercao digital - Desenvolvimento de WebSite</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>52999999000199</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>KICK OFF INVALIDO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bruno Henrique Santana Leal</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>amanha</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://invalid-kickoff.example/</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/tests/fixtures/control-sheet-cases.xlsx
+++ b/tests/fixtures/control-sheet-cases.xlsx
@@ -546,6 +546,51 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>012099/2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>40-2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Insercao digital - Desenvolvimento de WebSite</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>11222333000181</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>EMPRESA GEMEA LTDA</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Christian Albuquerque Alonso</t>
+        </is>
+      </c>
+      <c r="G14" s="1">
+        <v>46185</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://gemea.example/</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/tests/fixtures/control-sheet-cases.xlsx
+++ b/tests/fixtures/control-sheet-cases.xlsx
@@ -591,6 +591,51 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>012120/2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>45-2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Insercao digital - Desenvolvimento de WebSite</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>20517958000180</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LOJA SEM PROTOCOLO</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bruno Henrique Santana Leal</t>
+        </is>
+      </c>
+      <c r="G16" s="1">
+        <v>46162</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>www.exemplo.com.br</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/tests/fixtures/control-sheet-cases.xlsx
+++ b/tests/fixtures/control-sheet-cases.xlsx
@@ -445,7 +445,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://out-of-scope.example/</t>
+          <t>https://casanossa.example/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -631,6 +631,96 @@
         </is>
       </c>
       <c r="I16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>012140/2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>46-2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Implantacao de Loja Virtual</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>LOJA CNPJ INVALIDO</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Christian Albuquerque Alonso</t>
+        </is>
+      </c>
+      <c r="G17" s="1">
+        <v>46164</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://loja-invalida.example/</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>012160/2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>47-2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Servico sem Master aprovado</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>30129441000160</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SERVICO NAO CONTRATADO</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bruno Henrique Santana Leal</t>
+        </is>
+      </c>
+      <c r="G19" s="1">
+        <v>46168</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://out-of-scope.example/</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t/>
         </is>
